--- a/sharedata/excel/J-集市类型表(MarketTypeData).xlsx
+++ b/sharedata/excel/J-集市类型表(MarketTypeData).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\策划文档\配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,7 +15,6 @@
     <sheet name="集市类型表(MarketTypeData)" sheetId="1" r:id="rId1"/>
     <sheet name="集市商品栏位表(MarketSlotData)" sheetId="2" r:id="rId2"/>
     <sheet name="集市商品表(MarketGoodsData)" sheetId="3" r:id="rId3"/>
-    <sheet name="#首版待配置" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="109">
   <si>
     <t>每周期免费刷新固定1次，refresh_cost仅填付费档位，不含免费0。</t>
   </si>
@@ -148,6 +147,9 @@
     <t>每日商店</t>
   </si>
   <si>
+    <t>商店图标_每日商店</t>
+  </si>
+  <si>
     <t>钻石</t>
   </si>
   <si>
@@ -157,6 +159,9 @@
     <t>资源商店</t>
   </si>
   <si>
+    <t>商店图标_资源商店</t>
+  </si>
+  <si>
     <t>装备商店</t>
   </si>
   <si>
@@ -208,6 +213,30 @@
     <t>ref(BuildLevelData)</t>
   </si>
   <si>
+    <t>临时栏位_1001</t>
+  </si>
+  <si>
+    <t>临时每日经验池</t>
+  </si>
+  <si>
+    <t>临时栏位_1002</t>
+  </si>
+  <si>
+    <t>临时每日材料池</t>
+  </si>
+  <si>
+    <t>临时栏位_2001</t>
+  </si>
+  <si>
+    <t>临时资源木材池</t>
+  </si>
+  <si>
+    <t>临时栏位_2002</t>
+  </si>
+  <si>
+    <t>临时资源矿石池</t>
+  </si>
+  <si>
     <t>集市商品表</t>
   </si>
   <si>
@@ -289,94 +318,49 @@
     <t>ref_count(ItemData)</t>
   </si>
   <si>
-    <t>首版集市待配置清单（本页不参与导表）</t>
-  </si>
-  <si>
-    <t>维护位置</t>
-  </si>
-  <si>
-    <t>已确认范围</t>
-  </si>
-  <si>
-    <t>需要配置的内容</t>
-  </si>
-  <si>
-    <t>填写边界</t>
-  </si>
-  <si>
-    <t>每日商店、资源商店；每日排第一</t>
-  </si>
-  <si>
-    <t>正式记录、图标、入口条件、刷新周期、刷新消耗及费用、建筑减免开关</t>
-  </si>
-  <si>
-    <t>原测试ID与值保存在#原测试配置；未知值不按0或FALSE处理</t>
-  </si>
-  <si>
-    <t>分页下的固定栏位</t>
-  </si>
-  <si>
-    <t>栏位数量及ID、商品池、排序、功能/集市等级条件</t>
-  </si>
-  <si>
-    <t>同sort按字符串ID排序；不预设商品格数</t>
-  </si>
-  <si>
-    <t>每行一个商品候选</t>
-  </si>
-  <si>
-    <t>group_id/group_key、所属分页、商品及数量、单一货币、价格、折扣、限购、权重</t>
-  </si>
-  <si>
-    <t>组内归属一致；组键仅首行；商品与货币引用有效ItemData</t>
-  </si>
-  <si>
-    <t>FeatureData</t>
-  </si>
-  <si>
-    <t>入口与每日商店共用；资源页单独解锁</t>
-  </si>
-  <si>
-    <t>每日商店/资源商店正式功能记录、门槛与提示</t>
-  </si>
-  <si>
-    <t>见功能解锁簿#集市待配置，不另设重复入口条件</t>
-  </si>
-  <si>
-    <t>BuildLevelData</t>
-  </si>
-  <si>
-    <t>集市建筑、候选门槛、购买减免</t>
-  </si>
-  <si>
-    <t>首级建造及后续等级的条件、费用、时间、产出、减免率</t>
-  </si>
-  <si>
-    <t>见建筑簿#集市待配置；不复制其他建筑或旧项目数值</t>
-  </si>
-  <si>
-    <t>ItemData / IconData</t>
-  </si>
-  <si>
-    <t>商品、货币、分页图标</t>
-  </si>
-  <si>
-    <t>确定商品清单后登记本项目真实物品和资源</t>
-  </si>
-  <si>
-    <t>公共表尚待完善；不得复用旧项目资源ID假装已配齐</t>
-  </si>
-  <si>
-    <t>ParamData</t>
-  </si>
-  <si>
-    <t>market_min_price=1</t>
-  </si>
-  <si>
-    <t>无新增参数</t>
-  </si>
-  <si>
-    <t>沿用单份先向上取整、最低1，再乘份数；免费商品不使用</t>
+    <t>临时商品_1001_1</t>
+  </si>
+  <si>
+    <t>集市-1级</t>
+  </si>
+  <si>
+    <t>英雄经验//100</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>临时商品_1001_2</t>
+  </si>
+  <si>
+    <t>士兵经验//100</t>
+  </si>
+  <si>
+    <t>临时商品_1002_1</t>
+  </si>
+  <si>
+    <t>突破符石//5</t>
+  </si>
+  <si>
+    <t>临时商品_1002_2</t>
+  </si>
+  <si>
+    <t>英雄招募券//1</t>
+  </si>
+  <si>
+    <t>临时商品_2001_1</t>
+  </si>
+  <si>
+    <t>集市-2级</t>
+  </si>
+  <si>
+    <t>木材//100</t>
+  </si>
+  <si>
+    <t>临时商品_2002_1</t>
+  </si>
+  <si>
+    <t>矿石//100</t>
   </si>
 </sst>
 </file>
@@ -405,6 +389,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -569,13 +560,6 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-      <b/>
-      <color rgb="FFFF0000"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -903,186 +887,195 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyFill="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="53">
@@ -1561,255 +1554,255 @@
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="15.2222222222222" style="6" customWidth="1"/>
-    <col min="2" max="2" width="6.44444444444444" style="6" customWidth="1"/>
-    <col min="3" max="3" width="9.55555555555556" style="6" customWidth="1"/>
-    <col min="4" max="4" width="14.2222222222222" style="6" customWidth="1"/>
-    <col min="5" max="5" width="11.8888888888889" style="6" customWidth="1"/>
-    <col min="6" max="6" width="14.7777777777778" style="6" customWidth="1"/>
-    <col min="7" max="7" width="16.7777777777778" style="6" customWidth="1"/>
-    <col min="8" max="8" width="12.1111111111111" style="6" customWidth="1"/>
-    <col min="9" max="9" width="16.8888888888889" style="6" customWidth="1"/>
-    <col min="10" max="10" width="20.2222222222222" style="6" customWidth="1"/>
-    <col min="11" max="11" width="7.88888888888889" style="6" customWidth="1"/>
-    <col min="12" max="16383" width="9" style="6" customWidth="1"/>
-    <col min="16384" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="15.2222222222222" style="7" customWidth="1"/>
+    <col min="2" max="2" width="6.44444444444444" style="7" customWidth="1"/>
+    <col min="3" max="3" width="9.55555555555556" style="7" customWidth="1"/>
+    <col min="4" max="4" width="14.4444444444444" style="7" customWidth="1"/>
+    <col min="5" max="5" width="15.8888888888889" style="7" customWidth="1"/>
+    <col min="6" max="6" width="14.7777777777778" style="7" customWidth="1"/>
+    <col min="7" max="7" width="13.3333333333333" style="7" customWidth="1"/>
+    <col min="8" max="8" width="12.1111111111111" style="7" customWidth="1"/>
+    <col min="9" max="9" width="17.6666666666667" style="7" customWidth="1"/>
+    <col min="10" max="10" width="20.2222222222222" style="7" customWidth="1"/>
+    <col min="11" max="11" width="7.88888888888889" style="7" customWidth="1"/>
+    <col min="12" max="16383" width="9" style="7" customWidth="1"/>
+    <col min="16384" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" spans="1:11">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="6" customFormat="1" spans="1:11">
+      <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" s="3" customFormat="1" spans="1:11">
-      <c r="A4" s="5" t="s">
+    <row r="4" s="6" customFormat="1" spans="1:11">
+      <c r="A4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" s="3" customFormat="1" spans="1:11">
-      <c r="A5" s="5" t="s">
+    <row r="5" s="6" customFormat="1" spans="1:11">
+      <c r="A5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:11">
-      <c r="A6" s="5" t="s">
+    <row r="6" s="6" customFormat="1" spans="1:11">
+      <c r="A6" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5" t="s">
+      <c r="D6" s="10"/>
+      <c r="E6" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5" t="s">
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="33.0" customHeight="1">
+    <row r="7" spans="1:11">
       <c r="A7"/>
-      <c r="B7" s="7">
+      <c r="B7" s="11">
         <v>1</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="8" t="str">
+      <c r="D7" s="11" t="str">
         <f>"$Lang$"&amp;C7</f>
         <v>$Lang$每日商店</v>
       </c>
-      <c r="E7" t="str" s="8">
-        <v>商店图标_每日商店</v>
-      </c>
-      <c r="F7" t="str" s="7">
-        <v>每日商店</v>
-      </c>
-      <c r="G7" t="n" s="7">
+      <c r="E7" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="11">
         <v>1</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="8" t="s">
+      <c r="H7" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J7" t="b" s="7">
+      <c r="I7" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="11">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="33.0" customHeight="1">
+    <row r="8" spans="1:11">
       <c r="A8"/>
-      <c r="B8" s="7">
+      <c r="B8" s="11">
         <v>2</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="8" t="str">
+      <c r="C8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="11" t="str">
         <f>"$Lang$"&amp;C8</f>
         <v>$Lang$资源商店</v>
       </c>
-      <c r="E8" t="str" s="8">
-        <v>商店图标_资源商店</v>
-      </c>
-      <c r="F8" t="str" s="7">
-        <v>资源商店</v>
-      </c>
-      <c r="G8" t="n" s="7">
+      <c r="E8" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="11">
         <v>1</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="8" t="s">
+      <c r="H8" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J8" t="b" s="7">
+      <c r="I8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="11">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="33.0" customHeight="1">
+    <row r="9" spans="1:11">
       <c r="A9"/>
-      <c r="B9" s="7">
+      <c r="B9" s="11">
         <v>3</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="8" t="str">
+      <c r="C9" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="11" t="str">
         <f>"$Lang$"&amp;C9</f>
         <v>$Lang$装备商店</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
-      <c r="H9" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="8" t="s">
+      <c r="H9" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J9" t="b" s="7">
+      <c r="I9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="11">
         <v>3</v>
       </c>
     </row>
@@ -1823,204 +1816,204 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="14.3333333333333" style="6" customWidth="1"/>
-    <col min="2" max="2" width="6.44444444444444" style="6" customWidth="1"/>
-    <col min="3" max="3" width="18.8888888888889" style="6" customWidth="1"/>
-    <col min="4" max="4" width="26.6666666666667" style="6" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="6" customWidth="1"/>
-    <col min="6" max="6" width="17.1111111111111" style="6" customWidth="1"/>
-    <col min="7" max="8" width="7.88888888888889" style="6" customWidth="1"/>
-    <col min="9" max="16382" width="9" style="6" customWidth="1"/>
-    <col min="16383" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="14.3333333333333" style="7" customWidth="1"/>
+    <col min="2" max="2" width="13" style="7" customWidth="1"/>
+    <col min="3" max="3" width="18.8888888888889" style="7" customWidth="1"/>
+    <col min="4" max="4" width="26.6666666666667" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="7" customWidth="1"/>
+    <col min="6" max="6" width="17.1111111111111" style="7" customWidth="1"/>
+    <col min="7" max="8" width="7.88888888888889" style="7" customWidth="1"/>
+    <col min="9" max="16382" width="9" style="7" customWidth="1"/>
+    <col min="16383" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" s="3" customFormat="1" spans="1:8">
-      <c r="A3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+    </row>
+    <row r="3" s="6" customFormat="1" spans="1:8">
+      <c r="A3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="C3" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="D3" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="E3" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="F3" s="9" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" s="3" customFormat="1" spans="1:8">
-      <c r="A4" s="5" t="s">
+      <c r="G3" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="H3" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" s="6" customFormat="1" spans="1:8">
+      <c r="A4" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="C4" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="F4" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" s="3" customFormat="1" spans="1:8">
-      <c r="A5" s="5" t="s">
+      <c r="H4" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" s="6" customFormat="1" spans="1:8">
+      <c r="A5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" spans="1:8">
-      <c r="A6" s="5" t="s">
+    <row r="6" s="6" customFormat="1" spans="1:8">
+      <c r="A6" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="C6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" ht="49.5" customHeight="1">
-      <c r="B7" t="str" s="8">
-        <v>临时栏位_1001</v>
-      </c>
-      <c r="C7" t="str" s="7">
-        <v>每日商店</v>
-      </c>
-      <c r="D7" t="str" s="7">
-        <v>临时每日经验池</v>
-      </c>
-      <c r="G7" t="n" s="7">
+      <c r="F6" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="B7" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="11">
         <v>1</v>
       </c>
-      <c r="H7" t="b" s="7">
+      <c r="H7" s="11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="49.5" customHeight="1">
-      <c r="B8" t="str" s="8">
-        <v>临时栏位_1002</v>
-      </c>
-      <c r="C8" t="str" s="7">
-        <v>每日商店</v>
-      </c>
-      <c r="D8" t="str" s="7">
-        <v>临时每日材料池</v>
-      </c>
-      <c r="G8" t="n" s="7">
+    <row r="8" spans="1:8">
+      <c r="B8" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="11">
         <v>2</v>
       </c>
-      <c r="H8" t="b" s="7">
+      <c r="H8" s="11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="49.5" customHeight="1">
-      <c r="B9" t="str" s="8">
-        <v>临时栏位_2001</v>
-      </c>
-      <c r="C9" t="str" s="7">
-        <v>资源商店</v>
-      </c>
-      <c r="D9" t="str" s="7">
-        <v>临时资源木材池</v>
-      </c>
-      <c r="G9" t="n" s="7">
+    <row r="9" spans="1:8">
+      <c r="B9" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="11">
         <v>1</v>
       </c>
-      <c r="H9" t="b" s="7">
+      <c r="H9" s="11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="49.5" customHeight="1">
-      <c r="B10" t="str" s="8">
-        <v>临时栏位_2002</v>
-      </c>
-      <c r="C10" t="str" s="7">
-        <v>资源商店</v>
-      </c>
-      <c r="D10" t="str" s="7">
-        <v>临时资源矿石池</v>
-      </c>
-      <c r="G10" t="n" s="7">
+    <row r="10" spans="1:8">
+      <c r="B10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="11">
         <v>2</v>
       </c>
-      <c r="H10" t="b" s="7">
+      <c r="H10" s="11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2034,481 +2027,482 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="16.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="6.44444444444444" customWidth="1"/>
-    <col min="3" max="3" width="8.55555555555556" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="9.77777777777778" customWidth="1"/>
-    <col min="6" max="6" width="18.8888888888889" customWidth="1"/>
-    <col min="7" max="7" width="17.1111111111111" customWidth="1"/>
-    <col min="8" max="8" width="18.1111111111111" customWidth="1"/>
-    <col min="9" max="9" width="12.1111111111111" customWidth="1"/>
-    <col min="10" max="10" width="9.88888888888889" customWidth="1"/>
-    <col min="11" max="12" width="11.3333333333333" customWidth="1"/>
-    <col min="13" max="15" width="7.88888888888889" customWidth="1"/>
+    <col min="1" max="1" width="15.3333333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.7777777777778" style="2" customWidth="1"/>
+    <col min="3" max="3" width="7.88888888888889" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.7777777777778" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.2222222222222" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.3333333333333" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.7777777777778" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.6666666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="11.2222222222222" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9.22222222222222" style="2" customWidth="1"/>
+    <col min="11" max="12" width="10.5555555555556" style="2" customWidth="1"/>
+    <col min="13" max="15" width="7.22222222222222" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
+      <c r="A1"/>
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
+      <c r="F1"/>
+      <c r="G1"/>
+      <c r="H1"/>
+      <c r="I1"/>
+      <c r="J1"/>
+      <c r="K1"/>
+      <c r="L1"/>
+      <c r="M1"/>
+      <c r="N1"/>
+      <c r="O1"/>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-    </row>
-    <row r="3" s="3" customFormat="1" spans="1:15">
-      <c r="A3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:15">
+      <c r="A3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:15">
+      <c r="A4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:15">
+      <c r="A5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:15">
+      <c r="A6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="H6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="B7" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1001</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="F7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J7" s="5">
+        <v>100</v>
+      </c>
+      <c r="K7" s="5">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1</v>
+      </c>
+      <c r="M7" s="5">
+        <v>100</v>
+      </c>
+      <c r="N7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="B8" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1001</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J8" s="5">
+        <v>100</v>
+      </c>
+      <c r="K8" s="5">
+        <v>1</v>
+      </c>
+      <c r="L8" s="5">
+        <v>1</v>
+      </c>
+      <c r="M8" s="5">
+        <v>100</v>
+      </c>
+      <c r="N8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="B9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1002</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="F9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" s="5">
+        <v>50</v>
+      </c>
+      <c r="K9" s="5">
+        <v>1</v>
+      </c>
+      <c r="L9" s="5">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5">
+        <v>100</v>
+      </c>
+      <c r="N9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="B10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1002</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" s="5">
+        <v>200</v>
+      </c>
+      <c r="K10" s="5">
+        <v>1</v>
+      </c>
+      <c r="L10" s="5">
+        <v>1</v>
+      </c>
+      <c r="M10" s="5">
+        <v>100</v>
+      </c>
+      <c r="N10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="B11" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2001</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K3" s="2" t="s">
+      <c r="F11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J11" s="5">
+        <v>200</v>
+      </c>
+      <c r="K11" s="5">
+        <v>1</v>
+      </c>
+      <c r="L11" s="5">
+        <v>1</v>
+      </c>
+      <c r="M11" s="5">
+        <v>100</v>
+      </c>
+      <c r="N11" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="B12" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2002</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" s="3" customFormat="1" spans="1:15">
-      <c r="A4" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" s="3" customFormat="1" spans="1:15">
-      <c r="A5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" spans="1:15">
-      <c r="A6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-    </row>
-    <row r="7" ht="49.5" customHeight="1">
-      <c r="B7" t="str" s="8">
-        <v>临时商品_1001_1</v>
-      </c>
-      <c r="C7" t="n" s="7">
-        <v>1001</v>
-      </c>
-      <c r="D7" t="str" s="8">
-        <v>临时商品_1001_1</v>
-      </c>
-      <c r="E7" t="str" s="8">
-        <v>临时每日经验池</v>
-      </c>
-      <c r="F7" t="str" s="7">
-        <v>每日商店</v>
-      </c>
-      <c r="G7" t="str" s="7">
-        <v>集市-1级</v>
-      </c>
-      <c r="H7" t="str" s="7">
-        <v>英雄经验//100</v>
-      </c>
-      <c r="I7" t="str" s="7">
-        <v>金币</v>
-      </c>
-      <c r="J7" t="n" s="7">
+      <c r="F12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J12" s="5">
+        <v>200</v>
+      </c>
+      <c r="K12" s="5">
+        <v>1</v>
+      </c>
+      <c r="L12" s="5">
+        <v>1</v>
+      </c>
+      <c r="M12" s="5">
         <v>100</v>
       </c>
-      <c r="K7" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n" s="7">
-        <v>100</v>
-      </c>
-      <c r="N7" t="b" s="7">
+      <c r="N12" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="O7" t="b" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="49.5" customHeight="1">
-      <c r="B8" t="str" s="8">
-        <v>临时商品_1001_2</v>
-      </c>
-      <c r="C8" t="n" s="7">
-        <v>1001</v>
-      </c>
-      <c r="D8" t="str" s="8">
-        <v>临时商品_1001_2</v>
-      </c>
-      <c r="F8" t="str" s="7">
-        <v>每日商店</v>
-      </c>
-      <c r="G8" t="str" s="7">
-        <v>集市-1级</v>
-      </c>
-      <c r="H8" t="str" s="7">
-        <v>士兵经验//100</v>
-      </c>
-      <c r="I8" t="str" s="7">
-        <v>金币</v>
-      </c>
-      <c r="J8" t="n" s="7">
-        <v>100</v>
-      </c>
-      <c r="K8" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n" s="7">
-        <v>100</v>
-      </c>
-      <c r="N8" t="b" s="7">
-        <v>0</v>
-      </c>
-      <c r="O8" t="b" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="49.5" customHeight="1">
-      <c r="B9" t="str" s="8">
-        <v>临时商品_1002_1</v>
-      </c>
-      <c r="C9" t="n" s="7">
-        <v>1002</v>
-      </c>
-      <c r="D9" t="str" s="8">
-        <v>临时商品_1002_1</v>
-      </c>
-      <c r="E9" t="str" s="8">
-        <v>临时每日材料池</v>
-      </c>
-      <c r="F9" t="str" s="7">
-        <v>每日商店</v>
-      </c>
-      <c r="G9" t="str" s="7">
-        <v>集市-1级</v>
-      </c>
-      <c r="H9" t="str" s="7">
-        <v>突破符石//5</v>
-      </c>
-      <c r="I9" t="str" s="7">
-        <v>钻石</v>
-      </c>
-      <c r="J9" t="n" s="7">
-        <v>50</v>
-      </c>
-      <c r="K9" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n" s="7">
-        <v>100</v>
-      </c>
-      <c r="N9" t="b" s="7">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="49.5" customHeight="1">
-      <c r="B10" t="str" s="8">
-        <v>临时商品_1002_2</v>
-      </c>
-      <c r="C10" t="n" s="7">
-        <v>1002</v>
-      </c>
-      <c r="D10" t="str" s="8">
-        <v>临时商品_1002_2</v>
-      </c>
-      <c r="F10" t="str" s="7">
-        <v>每日商店</v>
-      </c>
-      <c r="G10" t="str" s="7">
-        <v>集市-1级</v>
-      </c>
-      <c r="H10" t="str" s="7">
-        <v>英雄招募券//1</v>
-      </c>
-      <c r="I10" t="str" s="7">
-        <v>钻石</v>
-      </c>
-      <c r="J10" t="n" s="7">
-        <v>200</v>
-      </c>
-      <c r="K10" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n" s="7">
-        <v>100</v>
-      </c>
-      <c r="N10" t="b" s="7">
-        <v>0</v>
-      </c>
-      <c r="O10" t="b" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="49.5" customHeight="1">
-      <c r="B11" t="str" s="8">
-        <v>临时商品_2001_1</v>
-      </c>
-      <c r="C11" t="n" s="7">
-        <v>2001</v>
-      </c>
-      <c r="D11" t="str" s="8">
-        <v>临时商品_2001_1</v>
-      </c>
-      <c r="E11" t="str" s="8">
-        <v>临时资源木材池</v>
-      </c>
-      <c r="F11" t="str" s="7">
-        <v>资源商店</v>
-      </c>
-      <c r="G11" t="str" s="7">
-        <v>集市-2级</v>
-      </c>
-      <c r="H11" t="str" s="7">
-        <v>木材//100</v>
-      </c>
-      <c r="I11" t="str" s="7">
-        <v>金币</v>
-      </c>
-      <c r="J11" t="n" s="7">
-        <v>200</v>
-      </c>
-      <c r="K11" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n" s="7">
-        <v>100</v>
-      </c>
-      <c r="N11" t="b" s="7">
-        <v>0</v>
-      </c>
-      <c r="O11" t="b" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="49.5" customHeight="1">
-      <c r="B12" t="str" s="8">
-        <v>临时商品_2002_1</v>
-      </c>
-      <c r="C12" t="n" s="7">
-        <v>2002</v>
-      </c>
-      <c r="D12" t="str" s="8">
-        <v>临时商品_2002_1</v>
-      </c>
-      <c r="E12" t="str" s="8">
-        <v>临时资源矿石池</v>
-      </c>
-      <c r="F12" t="str" s="7">
-        <v>资源商店</v>
-      </c>
-      <c r="G12" t="str" s="7">
-        <v>集市-2级</v>
-      </c>
-      <c r="H12" t="str" s="7">
-        <v>矿石//100</v>
-      </c>
-      <c r="I12" t="str" s="7">
-        <v>金币</v>
-      </c>
-      <c r="J12" t="n" s="7">
-        <v>200</v>
-      </c>
-      <c r="K12" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n" s="7">
-        <v>100</v>
-      </c>
-      <c r="N12" t="b" s="7">
-        <v>0</v>
-      </c>
-      <c r="O12" t="b" s="7">
+      <c r="O12" s="5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2516,150 +2510,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="4" width="66" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="33" customHeight="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" customHeight="1" spans="1:4">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" ht="33" customHeight="1" spans="1:4">
-      <c r="A3" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" ht="33" customHeight="1" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" ht="33" customHeight="1" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" ht="33" customHeight="1" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" ht="33" customHeight="1" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" ht="33" customHeight="1" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" ht="33" customHeight="1" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>